--- a/Side Bar Files/GWD Data/BW Casing Pipes.xlsx
+++ b/Side Bar Files/GWD Data/BW Casing Pipes.xlsx
@@ -351,8 +351,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -371,7 +375,9 @@
     <xf numFmtId="4" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -795,7 +801,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480E9E22-D6A2-4DE8-8242-D7EB3583B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF68F3B2-14F6-4FB7-9455-0C11E99BB9A7}">
   <dimension ref="A1:F287"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/BW Casing Pipes.xlsx
+++ b/Side Bar Files/GWD Data/BW Casing Pipes.xlsx
@@ -9,18 +9,26 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+    <definedName name="DerivedRates">[1]Derived!$C:$C</definedName>
+    <definedName name="DerivedCodes">[1]Derived!$A:$A</definedName>
+  </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="59">
   <si>
     <t>Casing Pipe For Borewell , Tube Well And Filterpoint Well</t>
   </si>
   <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 140 mm 6 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 140 mm 6 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
   </si>
   <si>
     <t>Code</t>
@@ -104,7 +112,7 @@
     <t>Say</t>
   </si>
   <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 140 mm 8 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 140 mm 8 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
   </si>
   <si>
     <t>MR10225</t>
@@ -113,7 +121,7 @@
     <t>PVC Pipe, 8kg/cm2, 140mm Dia.</t>
   </si>
   <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 160mm 6 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 160mm 6 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
   </si>
   <si>
     <t>MR10216</t>
@@ -122,16 +130,16 @@
     <t>PVC Pipe, 6kg/cm2, 160mm Dia</t>
   </si>
   <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 180mm 6 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
-  </si>
-  <si>
-    <t>D</t>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 180mm 6 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+  </si>
+  <si>
+    <t>DL1</t>
   </si>
   <si>
     <t>PVC blind pipe 180 mm 6 Kg/cm2 dia as per IS: 4985</t>
   </si>
   <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 180mm 8 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 180mm 8 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
   </si>
   <si>
     <t>MR10228</t>
@@ -140,7 +148,7 @@
     <t>PVC Pipe, 8kg/cm2, 180mm Dia.</t>
   </si>
   <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 200mm 8 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 200mm 8 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
   </si>
   <si>
     <t>MR10227</t>
@@ -149,7 +157,7 @@
     <t>PVC Pipe, 8kg/cm2, 200mm Dia.</t>
   </si>
   <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 200mm 10 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 200mm 10 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
   </si>
   <si>
     <t>MR10240</t>
@@ -158,7 +166,7 @@
     <t>PVC Pipe, 10kg/cm2, 200mm Dia.</t>
   </si>
   <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 110 mm 6 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 110 mm 6 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
   </si>
   <si>
     <t>MR10214</t>
@@ -167,13 +175,16 @@
     <t>PVC Pipe, 6kg/cm2, 110mm Dia.</t>
   </si>
   <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 110 mm 4 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
-  </si>
-  <si>
-    <t>PVC Pipe, 4kg/cm2, 110mm Dia.</t>
-  </si>
-  <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 140 mm 10 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 110 mm 4 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+  </si>
+  <si>
+    <t>MR55</t>
+  </si>
+  <si>
+    <t>PVC pipe 110 mm outer dia. 4kgf/cm2</t>
+  </si>
+  <si>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 140 mm 10 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
   </si>
   <si>
     <t>MR10238</t>
@@ -182,7 +193,10 @@
     <t>PVC Pipe, 10kg/cm2, 140mm Dia.</t>
   </si>
   <si>
-    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 180mm 10 Kg/cm2 well casing  pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+    <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 180mm 10 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
+  </si>
+  <si>
+    <t>DL2</t>
   </si>
   <si>
     <t>PVC Pipe, 10kg/cm2, 180mm Dia.</t>
@@ -321,25 +335,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -420,11 +420,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -503,6 +503,113 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="GWD DR Abstract"/>
+      <sheetName val="GWD MR Abstract"/>
+      <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="ARS Filter Media"/>
+      <sheetName val="BW Casing Pipes"/>
+      <sheetName val="Electrical Essentials"/>
+      <sheetName val="GI on Wall PRICE"/>
+      <sheetName val="GI wo Trench"/>
+      <sheetName val="GI With Trench PRICE"/>
+      <sheetName val="GI Works"/>
+      <sheetName val="Gravel for TWC"/>
+      <sheetName val="Gutter&amp;Clamp"/>
+      <sheetName val="HP Erection and Pullout"/>
+      <sheetName val="HP Repair Labour"/>
+      <sheetName val="HP Repair Spares"/>
+      <sheetName val="Hydrants"/>
+      <sheetName val="Iron Structure"/>
+      <sheetName val="Lock"/>
+      <sheetName val="Metallic PH"/>
+      <sheetName val="Motor Starter GWD"/>
+      <sheetName val="Motor Starter Monoblock"/>
+      <sheetName val="Motor Starter PRICE"/>
+      <sheetName val="Other Fittings PRICE"/>
+      <sheetName val="Panel Board"/>
+      <sheetName val="Pump Cover"/>
+      <sheetName val="Pump Erection "/>
+      <sheetName val="Pump Pullout"/>
+      <sheetName val="PVC Fittings"/>
+      <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall (Concealed) PRICE"/>
+      <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
+      <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
+      <sheetName val="PVC With Trench"/>
+      <sheetName val="Scaffolding"/>
+      <sheetName val="Services"/>
+      <sheetName val="TW Casing Pipes"/>
+      <sheetName val="UG Cable PRICE"/>
+      <sheetName val="Water Meter"/>
+      <sheetName val="Water Tank"/>
+      <sheetName val="Well Protection"/>
+      <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
+      <sheetName val="ZCost Index"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -801,7 +908,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF68F3B2-14F6-4FB7-9455-0C11E99BB9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5F8DAE4-E484-4F1A-8DA4-5D23958DBAA6}">
   <dimension ref="A1:F287"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -881,11 +988,12 @@
         <v>100</v>
       </c>
       <c r="E6" s="11">
-        <v>475</v>
+        <f t="array" ref="E6">IFERROR(INDEX(LMRRates,MATCH(A6,LMRCodes,0),),)</f>
+        <v>284</v>
       </c>
       <c r="F6" s="12">
         <f>D6*E6</f>
-        <v>47500</v>
+        <v>28400</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="12.75">
@@ -898,7 +1006,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="12">
         <f>SUM(F6)</f>
-        <v>47500</v>
+        <v>28400</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="12.75">
@@ -911,7 +1019,7 @@
       <c r="E8" s="11"/>
       <c r="F8" s="12">
         <f>F7*1/100</f>
-        <v>475</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="12.75">
@@ -924,7 +1032,7 @@
       <c r="E9" s="11"/>
       <c r="F9" s="12">
         <f>SUM(F7:F8)</f>
-        <v>47975</v>
+        <v>28684</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="12.75">
@@ -937,7 +1045,7 @@
       <c r="E10" s="11"/>
       <c r="F10" s="12">
         <f>F9*0.15</f>
-        <v>7196.25</v>
+        <v>4302.60</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="12.75">
@@ -950,7 +1058,7 @@
       <c r="E11" s="11"/>
       <c r="F11" s="12">
         <f>SUM(F9:F10)</f>
-        <v>55171.25</v>
+        <v>32986.60</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="12.75">
@@ -963,7 +1071,7 @@
       <c r="E12" s="11"/>
       <c r="F12" s="12">
         <f>F11</f>
-        <v>55171.25</v>
+        <v>32986.60</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="12.75">
@@ -976,7 +1084,7 @@
       <c r="E13" s="11"/>
       <c r="F13" s="12">
         <f>MROUND((F12/100),0.05)</f>
-        <v>551.70</v>
+        <v>329.85</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="12.75">
@@ -1180,7 +1288,7 @@
     <row r="27" spans="1:6" ht="12.75">
       <c r="A27" s="14" t="str">
         <f>CONCATENATE("Say ",F13," + ",F26," x Cost Index")</f>
-        <v>Say 551.7 + 11.2 x Cost Index</v>
+        <v>Say 329.85 + 11.2 x Cost Index</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1254,11 +1362,12 @@
         <v>100</v>
       </c>
       <c r="E32" s="21">
-        <v>617</v>
+        <f t="array" ref="E32">IFERROR(INDEX(LMRRates,MATCH(A32,LMRCodes,0),),)</f>
+        <v>386</v>
       </c>
       <c r="F32" s="22">
         <f>D32*E32</f>
-        <v>61700</v>
+        <v>38600</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="12.75">
@@ -1271,7 +1380,7 @@
       <c r="E33" s="21"/>
       <c r="F33" s="22">
         <f>SUM(F32)</f>
-        <v>61700</v>
+        <v>38600</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="12.75">
@@ -1284,7 +1393,7 @@
       <c r="E34" s="21"/>
       <c r="F34" s="22">
         <f>F33*0.01</f>
-        <v>617</v>
+        <v>386</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="12.75">
@@ -1297,7 +1406,7 @@
       <c r="E35" s="21"/>
       <c r="F35" s="22">
         <f>SUM(F33:F34)</f>
-        <v>62317</v>
+        <v>38986</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="12.75">
@@ -1310,7 +1419,7 @@
       <c r="E36" s="21"/>
       <c r="F36" s="22">
         <f>F35*0.15</f>
-        <v>9347.55</v>
+        <v>5847.90</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="12.75">
@@ -1323,7 +1432,7 @@
       <c r="E37" s="21"/>
       <c r="F37" s="22">
         <f>SUM(F35:F36)</f>
-        <v>71664.55</v>
+        <v>44833.90</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="12.75">
@@ -1336,7 +1445,7 @@
       <c r="E38" s="21"/>
       <c r="F38" s="22">
         <f>F37</f>
-        <v>71664.55</v>
+        <v>44833.90</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="12.75">
@@ -1349,7 +1458,7 @@
       <c r="E39" s="21"/>
       <c r="F39" s="22">
         <f>MROUND((F38/100),0.05)</f>
-        <v>716.65</v>
+        <v>448.35</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="12.75">
@@ -1553,7 +1662,7 @@
     <row r="53" spans="1:6" ht="12.75">
       <c r="A53" s="14" t="str">
         <f>CONCATENATE("Say ",F39," + ",F52," x Cost Index")</f>
-        <v>Say 716.65 + 11.2 x Cost Index</v>
+        <v>Say 448.35 + 11.2 x Cost Index</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -1627,11 +1736,12 @@
         <v>100</v>
       </c>
       <c r="E58" s="11">
-        <v>613</v>
+        <f t="array" ref="E58">IFERROR(INDEX(LMRRates,MATCH(A58,LMRCodes,0),),)</f>
+        <v>372</v>
       </c>
       <c r="F58" s="12">
         <f>D58*E58</f>
-        <v>61300</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="12.75">
@@ -1644,7 +1754,7 @@
       <c r="E59" s="11"/>
       <c r="F59" s="12">
         <f>SUM(F58)</f>
-        <v>61300</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="12.75">
@@ -1657,7 +1767,7 @@
       <c r="E60" s="11"/>
       <c r="F60" s="12">
         <f>F59*0.01</f>
-        <v>613</v>
+        <v>372</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="12.75">
@@ -1670,7 +1780,7 @@
       <c r="E61" s="11"/>
       <c r="F61" s="12">
         <f>SUM(F59:F60)</f>
-        <v>61913</v>
+        <v>37572</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="12.75">
@@ -1685,7 +1795,7 @@
       <c r="E62" s="11"/>
       <c r="F62" s="12">
         <f>F61*0.15</f>
-        <v>9286.95</v>
+        <v>5635.80</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="12.75">
@@ -1700,7 +1810,7 @@
       <c r="E63" s="11"/>
       <c r="F63" s="12">
         <f>SUM(F61:F62)</f>
-        <v>71199.95</v>
+        <v>43207.80</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="12.75">
@@ -1715,7 +1825,7 @@
       <c r="E64" s="11"/>
       <c r="F64" s="12">
         <f>F63</f>
-        <v>71199.95</v>
+        <v>43207.80</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="12.75">
@@ -1728,7 +1838,7 @@
       <c r="E65" s="11"/>
       <c r="F65" s="12">
         <f>MROUND((F64/100),0.05)</f>
-        <v>712</v>
+        <v>432.10</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="12.75">
@@ -1932,7 +2042,7 @@
     <row r="79" spans="1:6" ht="12.75">
       <c r="A79" s="14" t="str">
         <f>CONCATENATE("Say ",F65," + ",F78," x Cost Index")</f>
-        <v>Say 712 + 11.2 x Cost Index</v>
+        <v>Say 432.1 + 11.2 x Cost Index</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -2006,11 +2116,12 @@
         <v>100</v>
       </c>
       <c r="E84" s="21">
-        <v>722</v>
+        <f t="array" ref="E84">IFERROR(INDEX(DerivedRates,MATCH(A84,DerivedCodes,0),),)</f>
+        <v>480</v>
       </c>
       <c r="F84" s="22">
         <f>D84*E84</f>
-        <v>72200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="12.75">
@@ -2023,7 +2134,7 @@
       <c r="E85" s="21"/>
       <c r="F85" s="22">
         <f>SUM(F84)</f>
-        <v>72200</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="12.75">
@@ -2036,7 +2147,7 @@
       <c r="E86" s="21"/>
       <c r="F86" s="22">
         <f>F85*0.01</f>
-        <v>722</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="12.75">
@@ -2049,7 +2160,7 @@
       <c r="E87" s="21"/>
       <c r="F87" s="22">
         <f>SUM(F85:F86)</f>
-        <v>72922</v>
+        <v>48480</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="12.75">
@@ -2062,7 +2173,7 @@
       <c r="E88" s="21"/>
       <c r="F88" s="22">
         <f>F87*0.15</f>
-        <v>10938.30</v>
+        <v>7272</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="12.75">
@@ -2075,7 +2186,7 @@
       <c r="E89" s="21"/>
       <c r="F89" s="22">
         <f>SUM(F87:F88)</f>
-        <v>83860.30</v>
+        <v>55752</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="12.75">
@@ -2088,7 +2199,7 @@
       <c r="E90" s="21"/>
       <c r="F90" s="22">
         <f>F89</f>
-        <v>83860.30</v>
+        <v>55752</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="12.75">
@@ -2101,7 +2212,7 @@
       <c r="E91" s="21"/>
       <c r="F91" s="22">
         <f>MROUND((F90/100),0.05)</f>
-        <v>838.60</v>
+        <v>557.50</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="12.75">
@@ -2305,7 +2416,7 @@
     <row r="105" spans="1:6" ht="12.75">
       <c r="A105" s="14" t="str">
         <f>CONCATENATE("Say ",F91," + ",F104," x Cost Index")</f>
-        <v>Say 838.6 + 11.2 x Cost Index</v>
+        <v>Say 557.5 + 11.2 x Cost Index</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -2379,11 +2490,12 @@
         <v>100</v>
       </c>
       <c r="E110" s="11">
-        <v>988</v>
+        <f t="array" ref="E110">IFERROR(INDEX(LMRRates,MATCH(A110,LMRCodes,0),),)</f>
+        <v>631</v>
       </c>
       <c r="F110" s="12">
         <f>D110*E110</f>
-        <v>98800</v>
+        <v>63100</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="12.75">
@@ -2396,7 +2508,7 @@
       <c r="E111" s="11"/>
       <c r="F111" s="12">
         <f>SUM(F110)</f>
-        <v>98800</v>
+        <v>63100</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="12.75">
@@ -2409,7 +2521,7 @@
       <c r="E112" s="11"/>
       <c r="F112" s="12">
         <f>F111*0.01</f>
-        <v>988</v>
+        <v>631</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="12.75">
@@ -2422,7 +2534,7 @@
       <c r="E113" s="11"/>
       <c r="F113" s="12">
         <f>SUM(F111:F112)</f>
-        <v>99788</v>
+        <v>63731</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="12.75">
@@ -2435,7 +2547,7 @@
       <c r="E114" s="11"/>
       <c r="F114" s="12">
         <f>F113*0.15</f>
-        <v>14968.20</v>
+        <v>9559.65</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="12.75">
@@ -2448,7 +2560,7 @@
       <c r="E115" s="11"/>
       <c r="F115" s="12">
         <f>SUM(F113:F114)</f>
-        <v>114756.20</v>
+        <v>73290.65</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="12.75">
@@ -2461,7 +2573,7 @@
       <c r="E116" s="11"/>
       <c r="F116" s="12">
         <f>F115</f>
-        <v>114756.20</v>
+        <v>73290.65</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="12.75">
@@ -2474,7 +2586,7 @@
       <c r="E117" s="11"/>
       <c r="F117" s="12">
         <f>MROUND((F116/100),0.05)</f>
-        <v>1147.55</v>
+        <v>732.90</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="12.75">
@@ -2678,7 +2790,7 @@
     <row r="131" spans="1:6" ht="12.75">
       <c r="A131" s="14" t="str">
         <f>CONCATENATE("Say ",F117," + ",F130," x Cost Index")</f>
-        <v>Say 1147.55 + 11.2 x Cost Index</v>
+        <v>Say 732.9 + 11.2 x Cost Index</v>
       </c>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -2752,11 +2864,12 @@
         <v>100</v>
       </c>
       <c r="E136" s="21">
-        <v>1240</v>
+        <f t="array" ref="E136">IFERROR(INDEX(LMRRates,MATCH(A136,LMRCodes,0),),)</f>
+        <v>770</v>
       </c>
       <c r="F136" s="22">
         <f>D136*E136</f>
-        <v>124000</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="12.75">
@@ -2769,7 +2882,7 @@
       <c r="E137" s="21"/>
       <c r="F137" s="22">
         <f>SUM(F136)</f>
-        <v>124000</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="12.75">
@@ -2782,7 +2895,7 @@
       <c r="E138" s="21"/>
       <c r="F138" s="22">
         <f>F137*0.01</f>
-        <v>1240</v>
+        <v>770</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="12.75">
@@ -2795,7 +2908,7 @@
       <c r="E139" s="21"/>
       <c r="F139" s="22">
         <f>SUM(F137:F138)</f>
-        <v>125240</v>
+        <v>77770</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="12.75">
@@ -2808,7 +2921,7 @@
       <c r="E140" s="21"/>
       <c r="F140" s="22">
         <f>F139*0.15</f>
-        <v>18786</v>
+        <v>11665.50</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="12.75">
@@ -2821,7 +2934,7 @@
       <c r="E141" s="21"/>
       <c r="F141" s="22">
         <f>SUM(F139:F140)</f>
-        <v>144026</v>
+        <v>89435.50</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="12.75">
@@ -2834,7 +2947,7 @@
       <c r="E142" s="21"/>
       <c r="F142" s="22">
         <f>F141</f>
-        <v>144026</v>
+        <v>89435.50</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="12.75">
@@ -2847,7 +2960,7 @@
       <c r="E143" s="21"/>
       <c r="F143" s="22">
         <f>MROUND((F142/100),0.05)</f>
-        <v>1440.25</v>
+        <v>894.35</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="12.75">
@@ -3050,7 +3163,7 @@
     <row r="157" spans="1:6" ht="12.75">
       <c r="A157" s="14" t="str">
         <f>CONCATENATE("Say ",F143," + ",F156," x Cost Index")</f>
-        <v>Say 1440.25 + 11.2 x Cost Index</v>
+        <v>Say 894.35 + 11.2 x Cost Index</v>
       </c>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -3124,11 +3237,12 @@
         <v>100</v>
       </c>
       <c r="E162" s="11">
-        <v>1529</v>
+        <f t="array" ref="E162">IFERROR(INDEX(LMRRates,MATCH(A162,LMRCodes,0),),)</f>
+        <v>957</v>
       </c>
       <c r="F162" s="12">
         <f>D162*E162</f>
-        <v>152900</v>
+        <v>95700</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="12.75">
@@ -3141,7 +3255,7 @@
       <c r="E163" s="11"/>
       <c r="F163" s="12">
         <f>SUM(F162)</f>
-        <v>152900</v>
+        <v>95700</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="12.75">
@@ -3154,7 +3268,7 @@
       <c r="E164" s="11"/>
       <c r="F164" s="12">
         <f>F163*0.01</f>
-        <v>1529</v>
+        <v>957</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="12.75">
@@ -3167,7 +3281,7 @@
       <c r="E165" s="11"/>
       <c r="F165" s="12">
         <f>SUM(F163:F164)</f>
-        <v>154429</v>
+        <v>96657</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="12.75">
@@ -3180,7 +3294,7 @@
       <c r="E166" s="11"/>
       <c r="F166" s="12">
         <f>F165*0.15</f>
-        <v>23164.35</v>
+        <v>14498.55</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="12.75">
@@ -3193,7 +3307,7 @@
       <c r="E167" s="11"/>
       <c r="F167" s="12">
         <f>SUM(F165:F166)</f>
-        <v>177593.35</v>
+        <v>111155.55</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="12.75">
@@ -3206,7 +3320,7 @@
       <c r="E168" s="11"/>
       <c r="F168" s="12">
         <f>F167</f>
-        <v>177593.35</v>
+        <v>111155.55</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="12.75">
@@ -3219,7 +3333,7 @@
       <c r="E169" s="11"/>
       <c r="F169" s="12">
         <f>MROUND((F168/100),0.05)</f>
-        <v>1775.95</v>
+        <v>1111.55</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="12.75">
@@ -3422,7 +3536,7 @@
     <row r="183" spans="1:6" ht="12.75">
       <c r="A183" s="14" t="str">
         <f>CONCATENATE("Say ",F169," + ",F182," x Cost Index")</f>
-        <v>Say 1775.95 + 11.2 x Cost Index</v>
+        <v>Say 1111.55 + 11.2 x Cost Index</v>
       </c>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -3496,11 +3610,12 @@
         <v>100</v>
       </c>
       <c r="E188" s="21">
-        <v>285</v>
+        <f t="array" ref="E188">IFERROR(INDEX(LMRRates,MATCH(A188,LMRCodes,0),),)</f>
+        <v>180</v>
       </c>
       <c r="F188" s="22">
         <f>D188*E188</f>
-        <v>28500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="12.75">
@@ -3513,7 +3628,7 @@
       <c r="E189" s="21"/>
       <c r="F189" s="22">
         <f>SUM(F188)</f>
-        <v>28500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="12.75">
@@ -3526,7 +3641,7 @@
       <c r="E190" s="21"/>
       <c r="F190" s="22">
         <f>F189*0.01</f>
-        <v>285</v>
+        <v>180</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="12.75">
@@ -3539,7 +3654,7 @@
       <c r="E191" s="21"/>
       <c r="F191" s="22">
         <f>SUM(F189:F190)</f>
-        <v>28785</v>
+        <v>18180</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="12.75">
@@ -3552,7 +3667,7 @@
       <c r="E192" s="21"/>
       <c r="F192" s="22">
         <f>F191*0.15</f>
-        <v>4317.75</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="12.75">
@@ -3565,7 +3680,7 @@
       <c r="E193" s="21"/>
       <c r="F193" s="22">
         <f>SUM(F191:F192)</f>
-        <v>33102.75</v>
+        <v>20907</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="12.75">
@@ -3578,7 +3693,7 @@
       <c r="E194" s="21"/>
       <c r="F194" s="22">
         <f>F193</f>
-        <v>33102.75</v>
+        <v>20907</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="12.75">
@@ -3591,7 +3706,7 @@
       <c r="E195" s="21"/>
       <c r="F195" s="22">
         <f>MROUND((F194/100),0.05)</f>
-        <v>331.05</v>
+        <v>209.05</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="12.75">
@@ -3795,7 +3910,7 @@
     <row r="209" spans="1:6" ht="12.75">
       <c r="A209" s="14" t="str">
         <f>CONCATENATE("Say ",F195," + ",F208," x Cost Index")</f>
-        <v>Say 331.05 + 11.2 x Cost Index</v>
+        <v>Say 209.05 + 11.2 x Cost Index</v>
       </c>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -3857,10 +3972,10 @@
     </row>
     <row r="214" spans="1:6" ht="12.75">
       <c r="A214" s="11" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C214" s="11" t="s">
         <v>12</v>
@@ -3869,11 +3984,11 @@
         <v>100</v>
       </c>
       <c r="E214" s="11">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F214" s="12">
         <f>D214*E214</f>
-        <v>19100</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="12.75">
@@ -3886,7 +4001,7 @@
       <c r="E215" s="11"/>
       <c r="F215" s="12">
         <f>SUM(F214)</f>
-        <v>19100</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="12.75">
@@ -3899,7 +4014,7 @@
       <c r="E216" s="11"/>
       <c r="F216" s="12">
         <f>F215*0.01</f>
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="12.75">
@@ -3912,7 +4027,7 @@
       <c r="E217" s="11"/>
       <c r="F217" s="12">
         <f>SUM(F215:F216)</f>
-        <v>19291</v>
+        <v>17170</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="12.75">
@@ -3925,7 +4040,7 @@
       <c r="E218" s="11"/>
       <c r="F218" s="12">
         <f>F217*0.15</f>
-        <v>2893.65</v>
+        <v>2575.50</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="12.75">
@@ -3938,7 +4053,7 @@
       <c r="E219" s="11"/>
       <c r="F219" s="12">
         <f>SUM(F217:F218)</f>
-        <v>22184.65</v>
+        <v>19745.50</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="12.75">
@@ -3951,7 +4066,7 @@
       <c r="E220" s="11"/>
       <c r="F220" s="12">
         <f>F219</f>
-        <v>22184.65</v>
+        <v>19745.50</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="12.75">
@@ -3964,7 +4079,7 @@
       <c r="E221" s="11"/>
       <c r="F221" s="12">
         <f>MROUND((F220/100),0.05)</f>
-        <v>221.85</v>
+        <v>197.45</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="12.75">
@@ -4168,7 +4283,7 @@
     <row r="235" spans="1:6" ht="12.75">
       <c r="A235" s="14" t="str">
         <f>CONCATENATE("Say ",F221," + ",F234," x Cost Index")</f>
-        <v>Say 221.85 + 11.2 x Cost Index</v>
+        <v>Say 197.45 + 11.2 x Cost Index</v>
       </c>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -4181,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="B236" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
@@ -4230,10 +4345,10 @@
     </row>
     <row r="240" spans="1:6" ht="12.75">
       <c r="A240" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B240" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C240" s="21" t="s">
         <v>12</v>
@@ -4242,11 +4357,12 @@
         <v>100</v>
       </c>
       <c r="E240" s="21">
-        <v>744</v>
+        <f t="array" ref="E240">IFERROR(INDEX(LMRRates,MATCH(A240,LMRCodes,0),),)</f>
+        <v>467</v>
       </c>
       <c r="F240" s="22">
         <f>D240*E240</f>
-        <v>74400</v>
+        <v>46700</v>
       </c>
     </row>
     <row r="241" spans="1:6" ht="12.75">
@@ -4259,7 +4375,7 @@
       <c r="E241" s="21"/>
       <c r="F241" s="22">
         <f>SUM(F240)</f>
-        <v>74400</v>
+        <v>46700</v>
       </c>
     </row>
     <row r="242" spans="1:6" ht="12.75">
@@ -4272,7 +4388,7 @@
       <c r="E242" s="21"/>
       <c r="F242" s="22">
         <f>F241*0.01</f>
-        <v>744</v>
+        <v>467</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="12.75">
@@ -4285,7 +4401,7 @@
       <c r="E243" s="21"/>
       <c r="F243" s="22">
         <f>SUM(F241:F242)</f>
-        <v>75144</v>
+        <v>47167</v>
       </c>
     </row>
     <row r="244" spans="1:6" ht="12.75">
@@ -4298,7 +4414,7 @@
       <c r="E244" s="21"/>
       <c r="F244" s="22">
         <f>F243*0.15</f>
-        <v>11271.60</v>
+        <v>7075.05</v>
       </c>
     </row>
     <row r="245" spans="1:6" ht="12.75">
@@ -4311,7 +4427,7 @@
       <c r="E245" s="21"/>
       <c r="F245" s="22">
         <f>SUM(F243:F244)</f>
-        <v>86415.60</v>
+        <v>54242.05</v>
       </c>
     </row>
     <row r="246" spans="1:6" ht="12.75">
@@ -4324,7 +4440,7 @@
       <c r="E246" s="21"/>
       <c r="F246" s="22">
         <f>F245</f>
-        <v>86415.60</v>
+        <v>54242.05</v>
       </c>
     </row>
     <row r="247" spans="1:6" ht="12.75">
@@ -4337,7 +4453,7 @@
       <c r="E247" s="21"/>
       <c r="F247" s="22">
         <f>MROUND((F246/100),0.05)</f>
-        <v>864.15</v>
+        <v>542.40</v>
       </c>
     </row>
     <row r="248" spans="1:6" ht="12.75">
@@ -4541,7 +4657,7 @@
     <row r="261" spans="1:6" ht="12.75">
       <c r="A261" s="14" t="str">
         <f>CONCATENATE("Say ",F247," + ",F260," x Cost Index")</f>
-        <v>Say 864.15 + 11.2 x Cost Index</v>
+        <v>Say 542.4 + 11.2 x Cost Index</v>
       </c>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -4554,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
@@ -4603,10 +4719,10 @@
     </row>
     <row r="266" spans="1:6" ht="12.75">
       <c r="A266" s="11" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B266" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C266" s="11" t="s">
         <v>12</v>
@@ -4615,11 +4731,12 @@
         <v>100</v>
       </c>
       <c r="E266" s="11">
-        <v>1254</v>
+        <f t="array" ref="E266">IFERROR(INDEX(DerivedRates,MATCH(A266,DerivedCodes,0),),)</f>
+        <v>784</v>
       </c>
       <c r="F266" s="12">
         <f>D266*E266</f>
-        <v>125400</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="267" spans="1:6" ht="12.75">
@@ -4632,7 +4749,7 @@
       <c r="E267" s="11"/>
       <c r="F267" s="12">
         <f>SUM(F266)</f>
-        <v>125400</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="268" spans="1:6" ht="12.75">
@@ -4645,7 +4762,7 @@
       <c r="E268" s="11"/>
       <c r="F268" s="12">
         <f>F267*0.01</f>
-        <v>1254</v>
+        <v>784</v>
       </c>
     </row>
     <row r="269" spans="1:6" ht="12.75">
@@ -4658,7 +4775,7 @@
       <c r="E269" s="11"/>
       <c r="F269" s="12">
         <f>SUM(F267:F268)</f>
-        <v>126654</v>
+        <v>79184</v>
       </c>
     </row>
     <row r="270" spans="1:6" ht="12.75">
@@ -4671,7 +4788,7 @@
       <c r="E270" s="11"/>
       <c r="F270" s="12">
         <f>F269*0.15</f>
-        <v>18998.10</v>
+        <v>11877.60</v>
       </c>
     </row>
     <row r="271" spans="1:6" ht="12.75">
@@ -4684,7 +4801,7 @@
       <c r="E271" s="11"/>
       <c r="F271" s="12">
         <f>SUM(F269:F270)</f>
-        <v>145652.10</v>
+        <v>91061.60</v>
       </c>
     </row>
     <row r="272" spans="1:6" ht="12.75">
@@ -4697,7 +4814,7 @@
       <c r="E272" s="11"/>
       <c r="F272" s="12">
         <f>F271</f>
-        <v>145652.10</v>
+        <v>91061.60</v>
       </c>
     </row>
     <row r="273" spans="1:6" ht="12.75">
@@ -4710,7 +4827,7 @@
       <c r="E273" s="11"/>
       <c r="F273" s="12">
         <f>MROUND((F272/100),0.05)</f>
-        <v>1456.50</v>
+        <v>910.60</v>
       </c>
     </row>
     <row r="274" spans="1:6" ht="12.75">
@@ -4914,7 +5031,7 @@
     <row r="287" spans="1:6" ht="12.75">
       <c r="A287" s="14" t="str">
         <f>CONCATENATE("Say ",F273," + ",F286," x Cost Index")</f>
-        <v>Say 1456.5 + 11.2 x Cost Index</v>
+        <v>Say 910.6 + 11.2 x Cost Index</v>
       </c>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>

--- a/Side Bar Files/GWD Data/BW Casing Pipes.xlsx
+++ b/Side Bar Files/GWD Data/BW Casing Pipes.xlsx
@@ -908,7 +908,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5F8DAE4-E484-4F1A-8DA4-5D23958DBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5466DA2-216C-4758-A007-073CD09EBAA6}">
   <dimension ref="A1:F287"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/BW Casing Pipes.xlsx
+++ b/Side Bar Files/GWD Data/BW Casing Pipes.xlsx
@@ -13,10 +13,10 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
-    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
-    <definedName name="DerivedRates">[1]Derived!$C:$C</definedName>
-    <definedName name="DerivedCodes">[1]Derived!$A:$A</definedName>
+    <definedName name="LMRRates">[1]zLMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]zLMR!$A:$A</definedName>
+    <definedName name="DerivedRates">[1]zDerived!$D:$D</definedName>
+    <definedName name="DerivedCodes">[1]zDerived!$A:$A</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -136,7 +136,7 @@
     <t>DL1</t>
   </si>
   <si>
-    <t>PVC blind pipe 180 mm 6 Kg/cm2 dia as per IS: 4985</t>
+    <t>PVC Pipe, 6kg/cm2, 180mm Dia.</t>
   </si>
   <si>
     <t>Supplying, assembling, lowering and fixing in vertical position in Borewell, PVC 180mm 8 Kg/cm2 well casing pipe of required dia, conforming to IS : 4985:2000, including required hire and labour charges, fittings &amp; accessories etc. all complete, for all depths, as per direction of Engineer- in- Charge.</t>
@@ -553,10 +553,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -908,7 +908,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5466DA2-216C-4758-A007-073CD09EBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7C2E4E-A1D2-4EDF-B384-73F6C6F1BAA6}">
   <dimension ref="A1:F287"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
